--- a/Excel/Practice/Case Study 2(Pivot Table).xlsx
+++ b/Excel/Practice/Case Study 2(Pivot Table).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A19F92-8784-4BDD-B9A8-C57E5BBB4A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D55CE42-FB3C-4A6F-AE91-EBA4A879D38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{3C2F27DB-59A7-4E77-BCCC-EA28361B83B3}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId4"/>
-    <pivotCache cacheId="10" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="62">
   <si>
     <t>Company</t>
   </si>
@@ -215,6 +215,9 @@
   <si>
     <t>Average of Quantity</t>
   </si>
+  <si>
+    <t>Max of Sales USD</t>
+  </si>
 </sst>
 </file>
 
@@ -265,7 +268,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -393,123 +396,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -560,16 +452,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -577,6 +459,10 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 1 2" xfId="1" xr:uid="{B1476517-8384-4BE4-9D5E-6902BBA44473}"/>
@@ -1004,7 +890,36 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Document Date" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2020-06-01T00:00:00" maxDate="2020-07-01T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2020-06-01T00:00:00" maxDate="2020-07-01T00:00:00" count="28">
+        <d v="2020-06-01T00:00:00"/>
+        <d v="2020-06-02T00:00:00"/>
+        <d v="2020-06-07T00:00:00"/>
+        <d v="2020-06-08T00:00:00"/>
+        <d v="2020-06-09T00:00:00"/>
+        <d v="2020-06-10T00:00:00"/>
+        <d v="2020-06-11T00:00:00"/>
+        <d v="2020-06-12T00:00:00"/>
+        <d v="2020-06-13T00:00:00"/>
+        <d v="2020-06-14T00:00:00"/>
+        <d v="2020-06-15T00:00:00"/>
+        <d v="2020-06-16T00:00:00"/>
+        <d v="2020-06-03T00:00:00"/>
+        <d v="2020-06-04T00:00:00"/>
+        <d v="2020-06-05T00:00:00"/>
+        <d v="2020-06-06T00:00:00"/>
+        <d v="2020-06-17T00:00:00"/>
+        <d v="2020-06-18T00:00:00"/>
+        <d v="2020-06-19T00:00:00"/>
+        <d v="2020-06-20T00:00:00"/>
+        <d v="2020-06-21T00:00:00"/>
+        <d v="2020-06-22T00:00:00"/>
+        <d v="2020-06-23T00:00:00"/>
+        <d v="2020-06-25T00:00:00"/>
+        <d v="2020-06-29T00:00:00"/>
+        <d v="2020-06-30T00:00:00"/>
+        <d v="2020-06-24T00:00:00"/>
+        <d v="2020-06-26T00:00:00"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Customer Code" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="8010" maxValue="8060"/>
@@ -2432,7 +2347,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <d v="2020-06-01T00:00:00"/>
+    <x v="0"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="103"/>
@@ -2445,7 +2360,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <d v="2020-06-02T00:00:00"/>
+    <x v="1"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="104"/>
@@ -2458,7 +2373,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
-    <d v="2020-06-01T00:00:00"/>
+    <x v="0"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="103"/>
@@ -2471,7 +2386,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
-    <d v="2020-06-02T00:00:00"/>
+    <x v="1"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="104"/>
@@ -2484,7 +2399,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
-    <d v="2020-06-01T00:00:00"/>
+    <x v="0"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="103"/>
@@ -2497,7 +2412,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
-    <d v="2020-06-02T00:00:00"/>
+    <x v="1"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="104"/>
@@ -2510,7 +2425,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="2"/>
-    <d v="2020-06-07T00:00:00"/>
+    <x v="2"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="105"/>
@@ -2523,7 +2438,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="3"/>
-    <d v="2020-06-08T00:00:00"/>
+    <x v="3"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="104"/>
@@ -2536,7 +2451,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="3"/>
-    <d v="2020-06-09T00:00:00"/>
+    <x v="4"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="105"/>
@@ -2549,7 +2464,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
-    <d v="2020-06-10T00:00:00"/>
+    <x v="5"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="104"/>
@@ -2562,7 +2477,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
-    <d v="2020-06-11T00:00:00"/>
+    <x v="6"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="105"/>
@@ -2575,7 +2490,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
-    <d v="2020-06-12T00:00:00"/>
+    <x v="7"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="107"/>
@@ -2588,7 +2503,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
-    <d v="2020-06-13T00:00:00"/>
+    <x v="8"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="104"/>
@@ -2601,7 +2516,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="4"/>
-    <d v="2020-06-14T00:00:00"/>
+    <x v="9"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="105"/>
@@ -2614,7 +2529,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <d v="2020-06-15T00:00:00"/>
+    <x v="10"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="103"/>
@@ -2627,7 +2542,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="5"/>
-    <d v="2020-06-16T00:00:00"/>
+    <x v="11"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="104"/>
@@ -2640,7 +2555,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
-    <d v="2020-06-02T00:00:00"/>
+    <x v="1"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="103"/>
@@ -2653,7 +2568,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
-    <d v="2020-06-03T00:00:00"/>
+    <x v="12"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="104"/>
@@ -2666,7 +2581,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
-    <d v="2020-06-04T00:00:00"/>
+    <x v="13"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="105"/>
@@ -2679,7 +2594,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
-    <d v="2020-06-05T00:00:00"/>
+    <x v="14"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="107"/>
@@ -2692,7 +2607,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="6"/>
-    <d v="2020-06-06T00:00:00"/>
+    <x v="15"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="103"/>
@@ -2705,7 +2620,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="7"/>
-    <d v="2020-06-10T00:00:00"/>
+    <x v="5"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="103"/>
@@ -2718,7 +2633,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="7"/>
-    <d v="2020-06-11T00:00:00"/>
+    <x v="6"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="104"/>
@@ -2731,7 +2646,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="8"/>
-    <d v="2020-06-12T00:00:00"/>
+    <x v="7"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="103"/>
@@ -2744,7 +2659,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="8"/>
-    <d v="2020-06-13T00:00:00"/>
+    <x v="8"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="104"/>
@@ -2757,7 +2672,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="9"/>
-    <d v="2020-06-14T00:00:00"/>
+    <x v="9"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="103"/>
@@ -2770,7 +2685,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="9"/>
-    <d v="2020-06-15T00:00:00"/>
+    <x v="10"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="104"/>
@@ -2783,7 +2698,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="9"/>
-    <d v="2020-06-16T00:00:00"/>
+    <x v="11"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="105"/>
@@ -2796,7 +2711,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="10"/>
-    <d v="2020-06-17T00:00:00"/>
+    <x v="16"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="104"/>
@@ -2809,7 +2724,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="10"/>
-    <d v="2020-06-18T00:00:00"/>
+    <x v="17"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="105"/>
@@ -2822,7 +2737,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="11"/>
-    <d v="2020-06-19T00:00:00"/>
+    <x v="18"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="104"/>
@@ -2835,7 +2750,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="11"/>
-    <d v="2020-06-20T00:00:00"/>
+    <x v="19"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="105"/>
@@ -2848,7 +2763,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="11"/>
-    <d v="2020-06-21T00:00:00"/>
+    <x v="20"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="107"/>
@@ -2861,7 +2776,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="12"/>
-    <d v="2020-06-15T00:00:00"/>
+    <x v="10"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="104"/>
@@ -2874,7 +2789,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="12"/>
-    <d v="2020-06-16T00:00:00"/>
+    <x v="11"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="105"/>
@@ -2887,7 +2802,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="13"/>
-    <d v="2020-06-17T00:00:00"/>
+    <x v="16"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="103"/>
@@ -2900,7 +2815,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="13"/>
-    <d v="2020-06-18T00:00:00"/>
+    <x v="17"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="104"/>
@@ -2913,7 +2828,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="14"/>
-    <d v="2020-06-19T00:00:00"/>
+    <x v="18"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="103"/>
@@ -2926,7 +2841,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="14"/>
-    <d v="2020-06-20T00:00:00"/>
+    <x v="19"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="104"/>
@@ -2939,7 +2854,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="14"/>
-    <d v="2020-06-21T00:00:00"/>
+    <x v="20"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="105"/>
@@ -2952,7 +2867,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="15"/>
-    <d v="2020-06-22T00:00:00"/>
+    <x v="21"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="107"/>
@@ -2965,7 +2880,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="15"/>
-    <d v="2020-06-23T00:00:00"/>
+    <x v="22"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="103"/>
@@ -2978,7 +2893,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="16"/>
-    <d v="2020-06-01T00:00:00"/>
+    <x v="0"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="101"/>
@@ -2991,7 +2906,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="16"/>
-    <d v="2020-06-02T00:00:00"/>
+    <x v="1"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="102"/>
@@ -3004,7 +2919,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="16"/>
-    <d v="2020-06-03T00:00:00"/>
+    <x v="12"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="106"/>
@@ -3017,7 +2932,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="16"/>
-    <d v="2020-06-04T00:00:00"/>
+    <x v="13"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="108"/>
@@ -3030,7 +2945,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="17"/>
-    <d v="2020-06-05T00:00:00"/>
+    <x v="14"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="101"/>
@@ -3043,7 +2958,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="17"/>
-    <d v="2020-06-06T00:00:00"/>
+    <x v="15"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="108"/>
@@ -3056,7 +2971,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="17"/>
-    <d v="2020-06-07T00:00:00"/>
+    <x v="2"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="113"/>
@@ -3069,7 +2984,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
-    <d v="2020-06-08T00:00:00"/>
+    <x v="3"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="114"/>
@@ -3082,7 +2997,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
-    <d v="2020-06-09T00:00:00"/>
+    <x v="4"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="101"/>
@@ -3095,7 +3010,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
-    <d v="2020-06-10T00:00:00"/>
+    <x v="5"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="102"/>
@@ -3108,7 +3023,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
-    <d v="2020-06-11T00:00:00"/>
+    <x v="6"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="106"/>
@@ -3121,7 +3036,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
-    <d v="2020-06-12T00:00:00"/>
+    <x v="7"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="108"/>
@@ -3134,7 +3049,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
-    <d v="2020-06-13T00:00:00"/>
+    <x v="8"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="117"/>
@@ -3147,7 +3062,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="18"/>
-    <d v="2020-06-14T00:00:00"/>
+    <x v="9"/>
     <n v="8020"/>
     <x v="1"/>
     <n v="118"/>
@@ -3160,7 +3075,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
-    <d v="2020-06-15T00:00:00"/>
+    <x v="10"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="118"/>
@@ -3173,7 +3088,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
-    <d v="2020-06-16T00:00:00"/>
+    <x v="11"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="117"/>
@@ -3186,7 +3101,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
-    <d v="2020-06-17T00:00:00"/>
+    <x v="16"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="118"/>
@@ -3199,7 +3114,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
-    <d v="2020-06-18T00:00:00"/>
+    <x v="17"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="116"/>
@@ -3212,7 +3127,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
-    <d v="2020-06-19T00:00:00"/>
+    <x v="18"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="106"/>
@@ -3225,7 +3140,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
-    <d v="2020-06-20T00:00:00"/>
+    <x v="19"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="101"/>
@@ -3238,7 +3153,7 @@
     <x v="1"/>
     <x v="0"/>
     <x v="19"/>
-    <d v="2020-06-21T00:00:00"/>
+    <x v="20"/>
     <n v="8010"/>
     <x v="0"/>
     <n v="102"/>
@@ -3251,7 +3166,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="20"/>
-    <d v="2020-06-01T00:00:00"/>
+    <x v="0"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="108"/>
@@ -3264,7 +3179,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="20"/>
-    <d v="2020-06-02T00:00:00"/>
+    <x v="1"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="109"/>
@@ -3277,7 +3192,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="21"/>
-    <d v="2020-06-01T00:00:00"/>
+    <x v="0"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="108"/>
@@ -3290,7 +3205,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="21"/>
-    <d v="2020-06-02T00:00:00"/>
+    <x v="1"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="109"/>
@@ -3303,7 +3218,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="22"/>
-    <d v="2020-06-01T00:00:00"/>
+    <x v="0"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="108"/>
@@ -3316,7 +3231,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="22"/>
-    <d v="2020-06-02T00:00:00"/>
+    <x v="1"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="109"/>
@@ -3329,7 +3244,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="22"/>
-    <d v="2020-06-07T00:00:00"/>
+    <x v="2"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="110"/>
@@ -3342,7 +3257,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="23"/>
-    <d v="2020-06-08T00:00:00"/>
+    <x v="3"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="109"/>
@@ -3355,7 +3270,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="23"/>
-    <d v="2020-06-09T00:00:00"/>
+    <x v="4"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="110"/>
@@ -3368,7 +3283,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="24"/>
-    <d v="2020-06-08T00:00:00"/>
+    <x v="3"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="109"/>
@@ -3381,7 +3296,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="24"/>
-    <d v="2020-06-09T00:00:00"/>
+    <x v="4"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="110"/>
@@ -3394,7 +3309,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="24"/>
-    <d v="2020-06-12T00:00:00"/>
+    <x v="7"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="111"/>
@@ -3407,7 +3322,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="25"/>
-    <d v="2020-06-08T00:00:00"/>
+    <x v="3"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="109"/>
@@ -3420,7 +3335,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="25"/>
-    <d v="2020-06-09T00:00:00"/>
+    <x v="4"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="110"/>
@@ -3433,7 +3348,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="26"/>
-    <d v="2020-06-15T00:00:00"/>
+    <x v="10"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="108"/>
@@ -3446,7 +3361,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="26"/>
-    <d v="2020-06-16T00:00:00"/>
+    <x v="11"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="109"/>
@@ -3459,7 +3374,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="27"/>
-    <d v="2020-06-15T00:00:00"/>
+    <x v="10"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="108"/>
@@ -3472,7 +3387,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="27"/>
-    <d v="2020-06-16T00:00:00"/>
+    <x v="11"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="109"/>
@@ -3485,7 +3400,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="27"/>
-    <d v="2020-06-19T00:00:00"/>
+    <x v="18"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="110"/>
@@ -3498,7 +3413,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="28"/>
-    <d v="2020-06-15T00:00:00"/>
+    <x v="10"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="111"/>
@@ -3511,7 +3426,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="28"/>
-    <d v="2020-06-16T00:00:00"/>
+    <x v="11"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="108"/>
@@ -3524,7 +3439,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="29"/>
-    <d v="2020-06-18T00:00:00"/>
+    <x v="17"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="108"/>
@@ -3537,7 +3452,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="29"/>
-    <d v="2020-06-23T00:00:00"/>
+    <x v="22"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="109"/>
@@ -3550,7 +3465,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="30"/>
-    <d v="2020-06-16T00:00:00"/>
+    <x v="11"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="108"/>
@@ -3563,7 +3478,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="30"/>
-    <d v="2020-06-25T00:00:00"/>
+    <x v="23"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="109"/>
@@ -3576,7 +3491,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="31"/>
-    <d v="2020-06-16T00:00:00"/>
+    <x v="11"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="108"/>
@@ -3589,7 +3504,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="31"/>
-    <d v="2020-06-18T00:00:00"/>
+    <x v="17"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="109"/>
@@ -3602,7 +3517,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="31"/>
-    <d v="2020-06-23T00:00:00"/>
+    <x v="22"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="110"/>
@@ -3615,7 +3530,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="32"/>
-    <d v="2020-06-29T00:00:00"/>
+    <x v="24"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="109"/>
@@ -3628,7 +3543,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="32"/>
-    <d v="2020-06-30T00:00:00"/>
+    <x v="25"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="110"/>
@@ -3641,7 +3556,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="33"/>
-    <d v="2020-06-15T00:00:00"/>
+    <x v="10"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="109"/>
@@ -3654,7 +3569,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="33"/>
-    <d v="2020-06-16T00:00:00"/>
+    <x v="11"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="110"/>
@@ -3667,7 +3582,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="33"/>
-    <d v="2020-06-17T00:00:00"/>
+    <x v="16"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="111"/>
@@ -3680,7 +3595,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="34"/>
-    <d v="2020-06-18T00:00:00"/>
+    <x v="17"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="109"/>
@@ -3693,7 +3608,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="34"/>
-    <d v="2020-06-19T00:00:00"/>
+    <x v="18"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="110"/>
@@ -3706,7 +3621,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="35"/>
-    <d v="2020-06-20T00:00:00"/>
+    <x v="19"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="108"/>
@@ -3719,7 +3634,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="35"/>
-    <d v="2020-06-21T00:00:00"/>
+    <x v="20"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="109"/>
@@ -3732,7 +3647,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="36"/>
-    <d v="2020-06-22T00:00:00"/>
+    <x v="21"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="108"/>
@@ -3745,7 +3660,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="36"/>
-    <d v="2020-06-23T00:00:00"/>
+    <x v="22"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="109"/>
@@ -3758,7 +3673,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="36"/>
-    <d v="2020-06-24T00:00:00"/>
+    <x v="26"/>
     <n v="8060"/>
     <x v="2"/>
     <n v="110"/>
@@ -3771,7 +3686,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="37"/>
-    <d v="2020-06-25T00:00:00"/>
+    <x v="23"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="111"/>
@@ -3784,7 +3699,7 @@
     <x v="2"/>
     <x v="1"/>
     <x v="37"/>
-    <d v="2020-06-26T00:00:00"/>
+    <x v="27"/>
     <n v="8050"/>
     <x v="3"/>
     <n v="108"/>
@@ -3950,105 +3865,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{034B7A98-BB28-4190-9BD9-C83A04DE043A}" name="PivotTable5" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C45:E62" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="39">
-        <item x="16"/>
-        <item x="17"/>
-        <item x="19"/>
-        <item x="18"/>
-        <item x="29"/>
-        <item x="31"/>
-        <item x="30"/>
-        <item x="20"/>
-        <item x="22"/>
-        <item x="21"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="17">
-        <item h="1" x="7"/>
-        <item h="1" x="13"/>
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item h="1" x="9"/>
-        <item h="1" x="11"/>
-        <item h="1" x="10"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="14"/>
-        <item h="1" x="15"/>
-        <item h="1" x="12"/>
-        <item h="1" x="3"/>
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AACCF6B6-60A4-4BBC-A1F9-356327185768}" name="PivotTable4" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AACCF6B6-60A4-4BBC-A1F9-356327185768}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C28:E41" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -4200,8 +4017,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56832A3D-CC51-43C3-A550-585DAF56662E}" name="PivotTable3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56832A3D-CC51-43C3-A550-585DAF56662E}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C21:E24" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -4281,8 +4098,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D8C7B65-09A7-492D-B8EE-B250F4AD2284}" name="PivotTable2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D8C7B65-09A7-492D-B8EE-B250F4AD2284}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C11:E17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -4370,8 +4187,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96466FBF-C76D-4EEC-AD5C-FF791CEE1FAB}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96466FBF-C76D-4EEC-AD5C-FF791CEE1FAB}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C4:E7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -4416,6 +4233,354 @@
   <colItems count="2">
     <i>
       <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales USD" fld="10" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{49E8DF37-CCC4-4BFC-A053-BC30257E6647}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C60:E67" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="39">
+        <item x="16"/>
+        <item x="17"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="29"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" numFmtId="164" showAll="0" sortType="descending">
+      <items count="29">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="23"/>
+        <item x="27"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="1" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="3" item="26" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Max of Sales USD" fld="10" subtotal="max" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{034B7A98-BB28-4190-9BD9-C83A04DE043A}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C45:E56" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="39">
+        <item x="16"/>
+        <item x="17"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="29"/>
+        <item x="31"/>
+        <item x="30"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" numFmtId="164" showAll="0">
+      <items count="29">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="26"/>
+        <item x="23"/>
+        <item x="27"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="17">
+        <item h="1" x="7"/>
+        <item h="1" x="13"/>
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="11"/>
+        <item h="1" x="10"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item h="1" x="12"/>
+        <item h="1" x="3"/>
+        <item x="2"/>
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="13"/>
     </i>
     <i t="grand">
       <x/>
@@ -8893,28 +9058,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C6C6DF-0AD2-4DEA-9D47-53B920739A1E}">
-  <dimension ref="B3:G62"/>
+  <dimension ref="B3:G67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="74.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B3" s="28">
+      <c r="B3" s="18">
         <v>1</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C4" s="15" t="s">
@@ -8939,10 +9106,10 @@
       <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6">
         <v>66100</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6">
         <v>66100</v>
       </c>
     </row>
@@ -8950,24 +9117,24 @@
       <c r="C7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7">
         <v>66100</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7">
         <v>66100</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B10" s="28">
+      <c r="B10" s="18">
         <v>2</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C11" s="15" t="s">
@@ -8992,10 +9159,10 @@
       <c r="C13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13">
         <v>4</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13">
         <v>4</v>
       </c>
     </row>
@@ -9003,10 +9170,10 @@
       <c r="C14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14">
         <v>10</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14">
         <v>10</v>
       </c>
     </row>
@@ -9014,10 +9181,10 @@
       <c r="C15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15">
         <v>16</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15">
         <v>16</v>
       </c>
     </row>
@@ -9025,10 +9192,10 @@
       <c r="C16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16">
         <v>12</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16">
         <v>12</v>
       </c>
     </row>
@@ -9036,24 +9203,24 @@
       <c r="C17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17">
         <v>42</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B20" s="28">
+      <c r="B20" s="18">
         <v>3</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="C21" s="15" t="s">
@@ -9078,10 +9245,10 @@
       <c r="C23" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23">
         <v>880</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23">
         <v>880</v>
       </c>
     </row>
@@ -9089,18 +9256,18 @@
       <c r="C24" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24">
         <v>880</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24">
         <v>880</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="B27" s="28">
+      <c r="B27" s="18">
         <v>4</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -9127,10 +9294,10 @@
       <c r="C30" s="9">
         <v>25442</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30">
         <v>50</v>
       </c>
-      <c r="E30" s="27">
+      <c r="E30">
         <v>50</v>
       </c>
     </row>
@@ -9138,10 +9305,10 @@
       <c r="C31" s="9">
         <v>65629</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31">
         <v>153.33333333333334</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31">
         <v>153.33333333333334</v>
       </c>
     </row>
@@ -9149,10 +9316,10 @@
       <c r="C32" s="9">
         <v>65666</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32">
         <v>140</v>
       </c>
-      <c r="E32" s="27">
+      <c r="E32">
         <v>140</v>
       </c>
     </row>
@@ -9160,10 +9327,10 @@
       <c r="C33" s="9">
         <v>66015</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33">
         <v>140</v>
       </c>
-      <c r="E33" s="27">
+      <c r="E33">
         <v>140</v>
       </c>
     </row>
@@ -9171,10 +9338,10 @@
       <c r="C34" s="9">
         <v>66017</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34">
         <v>140</v>
       </c>
-      <c r="E34" s="27">
+      <c r="E34">
         <v>140</v>
       </c>
     </row>
@@ -9182,10 +9349,10 @@
       <c r="C35" s="9">
         <v>66030</v>
       </c>
-      <c r="D35" s="27">
+      <c r="D35">
         <v>135</v>
       </c>
-      <c r="E35" s="27">
+      <c r="E35">
         <v>135</v>
       </c>
     </row>
@@ -9193,10 +9360,10 @@
       <c r="C36" s="9">
         <v>66032</v>
       </c>
-      <c r="D36" s="27">
+      <c r="D36">
         <v>155</v>
       </c>
-      <c r="E36" s="27">
+      <c r="E36">
         <v>155</v>
       </c>
     </row>
@@ -9204,10 +9371,10 @@
       <c r="C37" s="9">
         <v>68097</v>
       </c>
-      <c r="D37" s="27">
+      <c r="D37">
         <v>135</v>
       </c>
-      <c r="E37" s="27">
+      <c r="E37">
         <v>135</v>
       </c>
     </row>
@@ -9215,10 +9382,10 @@
       <c r="C38" s="9">
         <v>68101</v>
       </c>
-      <c r="D38" s="27">
+      <c r="D38">
         <v>165</v>
       </c>
-      <c r="E38" s="27">
+      <c r="E38">
         <v>165</v>
       </c>
     </row>
@@ -9226,10 +9393,10 @@
       <c r="C39" s="9">
         <v>68112</v>
       </c>
-      <c r="D39" s="27">
+      <c r="D39">
         <v>150</v>
       </c>
-      <c r="E39" s="27">
+      <c r="E39">
         <v>150</v>
       </c>
     </row>
@@ -9237,10 +9404,10 @@
       <c r="C40" s="9">
         <v>68116</v>
       </c>
-      <c r="D40" s="27">
+      <c r="D40">
         <v>175</v>
       </c>
-      <c r="E40" s="27">
+      <c r="E40">
         <v>175</v>
       </c>
     </row>
@@ -9248,112 +9415,253 @@
       <c r="C41" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="27">
+      <c r="D41">
         <v>124.82758620689656</v>
       </c>
-      <c r="E41" s="27">
+      <c r="E41">
         <v>124.82758620689656</v>
       </c>
     </row>
     <row r="44" spans="2:5" ht="15" x14ac:dyDescent="0.3">
-      <c r="B44" s="28">
+      <c r="B44" s="18">
         <v>5</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C45" s="18"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="20"/>
+      <c r="C45" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C46" s="21"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="23"/>
+      <c r="C46" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C47" s="21"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="23"/>
+      <c r="C47" s="21">
+        <v>43986</v>
+      </c>
+      <c r="D47">
+        <v>1600</v>
+      </c>
+      <c r="E47">
+        <v>1600</v>
+      </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C48" s="21"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="23"/>
-    </row>
-    <row r="49" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C49" s="21"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="23"/>
-    </row>
-    <row r="50" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C50" s="21"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="23"/>
-    </row>
-    <row r="51" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C51" s="21"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="23"/>
-    </row>
-    <row r="52" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C52" s="21"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="23"/>
-    </row>
-    <row r="53" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C53" s="21"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="23"/>
-    </row>
-    <row r="54" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C54" s="21"/>
-      <c r="D54" s="22"/>
-      <c r="E54" s="23"/>
-    </row>
-    <row r="55" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C55" s="21"/>
-      <c r="D55" s="22"/>
-      <c r="E55" s="23"/>
-    </row>
-    <row r="56" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C56" s="21"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="23"/>
-    </row>
-    <row r="57" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C57" s="21"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="23"/>
-    </row>
-    <row r="58" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C58" s="21"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="23"/>
-    </row>
-    <row r="59" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C59" s="21"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="23"/>
-    </row>
-    <row r="60" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C60" s="21"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="23"/>
-    </row>
-    <row r="61" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C61" s="21"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="23"/>
-    </row>
-    <row r="62" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C62" s="24"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="26"/>
+      <c r="C48" s="21">
+        <v>43989</v>
+      </c>
+      <c r="D48">
+        <v>1000</v>
+      </c>
+      <c r="E48">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C49" s="21">
+        <v>43991</v>
+      </c>
+      <c r="D49">
+        <v>1200</v>
+      </c>
+      <c r="E49">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C50" s="21">
+        <v>43993</v>
+      </c>
+      <c r="D50">
+        <v>1900</v>
+      </c>
+      <c r="E50">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C51" s="21">
+        <v>43996</v>
+      </c>
+      <c r="D51">
+        <v>1900</v>
+      </c>
+      <c r="E51">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C52" s="21">
+        <v>43998</v>
+      </c>
+      <c r="D52">
+        <v>2600</v>
+      </c>
+      <c r="E52">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C53" s="21">
+        <v>44000</v>
+      </c>
+      <c r="D53">
+        <v>1300</v>
+      </c>
+      <c r="E53">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C54" s="21">
+        <v>44002</v>
+      </c>
+      <c r="D54">
+        <v>1400</v>
+      </c>
+      <c r="E54">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C55" s="21">
+        <v>44003</v>
+      </c>
+      <c r="D55">
+        <v>1400</v>
+      </c>
+      <c r="E55">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C56" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56">
+        <v>14300</v>
+      </c>
+      <c r="E56">
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C58" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="9">
+        <v>65666</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" ht="15" x14ac:dyDescent="0.3">
+      <c r="B59" s="18">
+        <v>6</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C60" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C61" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C62" s="21">
+        <v>43988</v>
+      </c>
+      <c r="D62" s="22">
+        <v>2400</v>
+      </c>
+      <c r="E62" s="22">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C63" s="21">
+        <v>43985</v>
+      </c>
+      <c r="D63" s="22">
+        <v>1680</v>
+      </c>
+      <c r="E63" s="22">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C64" s="21">
+        <v>43986</v>
+      </c>
+      <c r="D64" s="22">
+        <v>1600</v>
+      </c>
+      <c r="E64" s="22">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C65" s="21">
+        <v>43984</v>
+      </c>
+      <c r="D65" s="22">
+        <v>1440</v>
+      </c>
+      <c r="E65" s="22">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C66" s="21">
+        <v>43987</v>
+      </c>
+      <c r="D66" s="22">
+        <v>600</v>
+      </c>
+      <c r="E66" s="22">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="67" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C67" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" s="22">
+        <v>2400</v>
+      </c>
+      <c r="E67" s="22">
+        <v>2400</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>